--- a/src/main/resources/TestData/TestDataExcel.xlsx
+++ b/src/main/resources/TestData/TestDataExcel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ve00ym493\Downloads\pymidoliv\src\main\resources\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harish.kumar02\git\my-bitbucket-project\src\main\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BC844D-04A3-4EB5-BBBE-ABF4E2B6F148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661D07A2-F075-4A73-A003-16D9C4DC7A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,70 +25,64 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>TestCaseId</t>
   </si>
   <si>
-    <t>UserName</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
     <t>TestCase Description</t>
   </si>
   <si>
-    <t>Retrieve_01</t>
-  </si>
-  <si>
-    <t>User should get correct header inputs all the expected data should be retrieved and visible in table.</t>
-  </si>
-  <si>
-    <t>VE00YM493</t>
-  </si>
-  <si>
     <t>Harish</t>
   </si>
   <si>
-    <t>OpenFunction_01</t>
-  </si>
-  <si>
-    <t>User should be navigate to module detail page after clicking on Masters module.</t>
-  </si>
-  <si>
-    <t>Retrieve_02</t>
-  </si>
-  <si>
-    <t>Retrieve_03</t>
-  </si>
-  <si>
-    <t>User should not get any record and get validation message on retrieving from invalid training name.</t>
-  </si>
-  <si>
-    <t>VE00YM419</t>
-  </si>
-  <si>
-    <t>Submit_01</t>
-  </si>
-  <si>
-    <t>VE00AF943</t>
-  </si>
-  <si>
-    <t>User should able to submit the record.</t>
+    <t>checkout_01</t>
+  </si>
+  <si>
+    <t>standard_user</t>
+  </si>
+  <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>user should be able to bug a new product</t>
+  </si>
+  <si>
+    <t>firstname</t>
+  </si>
+  <si>
+    <t>lastname</t>
+  </si>
+  <si>
+    <t>portalcode</t>
+  </si>
+  <si>
+    <t>Tomar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF17C6A3"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -105,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -128,14 +122,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,96 +423,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
+      <c r="G2">
+        <v>245304</v>
       </c>
     </row>
   </sheetData>
